--- a/out/Attention-mamba2_repeat_2_000007.xlsx
+++ b/out/Attention-mamba2_repeat_2_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7867500136927614</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-0.0004500000027000205</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>5.187835348079873</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC40" t="n">
-        <v>-4.616200865339488e-05</v>
+        <v>10.38369030492118</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.05952544709415569</v>
+        <v>0.7779390749043589</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.05957160910280911</v>
+        <v>6.744770166508128</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.9726769118950123</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.05961399808914412</v>
+        <v>7.912308571120551</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.07076533769280823</v>
+        <v>1.394327740376901</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.08208687585378321</v>
+        <v>9.728836276799008</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09735797478896591</v>
+        <v>1.491654494064173</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2060459684934094</v>
+        <v>11.31792185444735</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1138169796531719</v>
+        <v>1.580853844566483</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3363301754622974</v>
+        <v>12.9880872269292</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05090003458773219</v>
+        <v>0.7134092722457261</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3242120078596599</v>
+        <v>12.83273957632558</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02450142134734622</v>
+        <v>0.344544714186787</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3222711331844358</v>
+        <v>12.80785898933161</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01161720209686237</v>
+        <v>0.1641652985608883</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.32098382303884</v>
+        <v>12.79137125599641</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003196984896886927</v>
+        <v>0.0486410328338602</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3157485646884015</v>
+        <v>12.72431315604289</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002208870056937108</v>
+        <v>0.0321737488925774</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3169677348336808</v>
+        <v>12.73999518519927</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001131590396621472</v>
+        <v>0.01646737896776692</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3170205523265952</v>
+        <v>12.74073130680554</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005781228823871956</v>
+        <v>0.008420762090542258</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3170444432584539</v>
+        <v>12.74109664669092</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002046875720674474</v>
+        <v>0.003162563378410797</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3168758411831372</v>
+        <v>12.73899437786623</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001109475188260492</v>
+        <v>0.001721737510402255</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.316892979397167</v>
+        <v>12.739272767641</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.084679245926485e-05</v>
+        <v>0.0008262875282840115</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3168829285748475</v>
+        <v>12.73920330854633</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.068162807157762e-05</v>
+        <v>0.000509608526418526</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3168934145653651</v>
+        <v>12.73939603880471</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.331395303104609e-05</v>
+        <v>0.0002646947192611883</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3168902537281362</v>
+        <v>12.73941453619832</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.854216248520305e-06</v>
+        <v>0.0001258812001328583</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3168846050064885</v>
+        <v>12.7394014350372</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>8.273743591478215e-07</v>
+        <v>7.814451455457625e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3168826815304042</v>
+        <v>12.73943306517152</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.844180684889389e-06</v>
+        <v>3.346517216201057e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3168769952528188</v>
+        <v>12.73942051611808</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.084302348447695e-06</v>
+        <v>1.146990651976723e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3168715847829012</v>
+        <v>12.73941099468651</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>3.901025847289637e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3168667501485827</v>
+        <v>12.73940740097106</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-1.124731583660385e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3168666061646752</v>
+        <v>12.73940110039691</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3168665834303738</v>
+        <v>12.73939598442047</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3168669017105906</v>
+        <v>12.73939193772672</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>-2.646054674377565e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3168679929570474</v>
+        <v>12.73938911737574</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.103542575915647</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3168673033499115</v>
+        <v>12.7393884277686</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3168673336623132</v>
+        <v>12.739388458081</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7867500136927614</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3168671442098031</v>
+        <v>12.73938826862849</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.316867197256506</v>
+        <v>12.7393883216752</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3168672503032088</v>
+        <v>12.7393883747219</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3168672124127068</v>
+        <v>12.7393883368314</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3168670835850002</v>
+        <v>12.73938820800369</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3168669396010926</v>
+        <v>12.73938806401978</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3168667804609842</v>
+        <v>12.73938790487967</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3168668335076871</v>
+        <v>12.73938795792638</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3168667804609842</v>
+        <v>12.73938790487967</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3168667804609842</v>
+        <v>12.73938790487967</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3168665985865747</v>
+        <v>12.73938772300527</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3168667653047834</v>
+        <v>12.73938788972347</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3168669623353937</v>
+        <v>12.73938808675408</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3168668031952854</v>
+        <v>12.73938792761398</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3168668410857874</v>
+        <v>12.73938796550448</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3168670381163975</v>
+        <v>12.73938816253509</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3168670153820964</v>
+        <v>12.73938813980079</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3168668638200886</v>
+        <v>12.73938798823878</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3168667880390845</v>
+        <v>12.73938791245778</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3168668865543897</v>
+        <v>12.73938801097308</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.31686689413249</v>
+        <v>12.73938801855118</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.316867159366004</v>
+        <v>12.73938828378469</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3168668638200886</v>
+        <v>12.73938798823878</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3168671063193013</v>
+        <v>12.73938823073799</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3168671896784057</v>
+        <v>12.73938831409709</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3168670229601969</v>
+        <v>12.73938814737889</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3168672124127068</v>
+        <v>12.7393883368314</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3168668638200886</v>
+        <v>12.73938798823878</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3168666592113779</v>
+        <v>12.73938778363007</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3168667728828839</v>
+        <v>12.73938789730157</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3168667880390845</v>
+        <v>12.73938791245778</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3168665531179723</v>
+        <v>12.73938767753666</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3168666137427755</v>
+        <v>12.73938773816147</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3168664849150689</v>
+        <v>12.73938760933376</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3168666213208758</v>
+        <v>12.73938774573957</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3168667956171851</v>
+        <v>12.73938792003587</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3168669396010926</v>
+        <v>12.73938806401978</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3168667728828839</v>
+        <v>12.73938789730157</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3168667653047834</v>
+        <v>12.73938788972347</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3168664773369683</v>
+        <v>12.73938760175566</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3168664924931692</v>
+        <v>12.73938761691186</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.316866719836181</v>
+        <v>12.73938784425487</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3168667046799802</v>
+        <v>12.73938782909867</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3168668107733857</v>
+        <v>12.73938793519208</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3168665379617715</v>
+        <v>12.73938766238046</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3168666364770767</v>
+        <v>12.73938776089577</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3168667880390845</v>
+        <v>12.73938791245778</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3168668031952854</v>
+        <v>12.73938792761398</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3168667804609842</v>
+        <v>12.73938790487967</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3168668638200886</v>
+        <v>12.73938798823878</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3168669623353937</v>
+        <v>12.73938808675408</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3168667956171851</v>
+        <v>12.73938792003587</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3168667804609842</v>
+        <v>12.73938790487967</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3168667501485827</v>
+        <v>12.73938787456727</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3168667349923819</v>
+        <v>12.73938785941107</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3168667728828839</v>
+        <v>12.73938789730157</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3168667880390845</v>
+        <v>12.73938791245778</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3168667804609842</v>
+        <v>12.73938790487967</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000007.xlsx
+++ b/out/Attention-mamba2_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030931</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.503542575915647</v>
+        <v>-1.076714909199301</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.503542575915647</v>
+        <v>-1.076714909199301</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.503542575915647</v>
+        <v>-1.076714909199301</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-6.056051339837722e-06</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.03043670499242308</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC40" t="n">
-        <v>-4.616200865339488e-05</v>
+        <v>0.06091719527034532</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.05952544709415569</v>
+        <v>0.004560887590957888</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.05957160910280911</v>
+        <v>0.03956454121573164</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.005703547543501493</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.05961399808914412</v>
+        <v>0.04641139676590881</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.07076533769280823</v>
+        <v>0.008178153438887448</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.08208687585378321</v>
+        <v>0.05706661903728824</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09735797478896591</v>
+        <v>0.008749296763472815</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2060459684934094</v>
+        <v>0.06638754706979776</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1138169796531719</v>
+        <v>0.009272762305562895</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3363301754622974</v>
+        <v>0.07618430470531061</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05090003458773219</v>
+        <v>0.004181882781166383</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3242120078596599</v>
+        <v>0.07526914200423401</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02450142134734622</v>
+        <v>0.002016429868951753</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3222711331844358</v>
+        <v>0.07511878078328887</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01161720209686237</v>
+        <v>0.0009587643781952644</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.503542575915647</v>
+        <v>0.2445617031931145</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.32098382303884</v>
+        <v>0.07501730829134468</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003196984896886927</v>
+        <v>0.0002805572939597059</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931145</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3157485646884015</v>
+        <v>0.07461883747746213</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002208870056937108</v>
+        <v>0.0001834046270923276</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3169677348336808</v>
+        <v>0.07470593202662747</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001131590396621472</v>
+        <v>9.142760150863396e-05</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3170205523265952</v>
+        <v>0.07470529328643065</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005781228823871956</v>
+        <v>4.432644473555205e-05</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3170444432584539</v>
+        <v>0.07470248394670594</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002046875720674474</v>
+        <v>1.392212292957465e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.3168758411831372</v>
+        <v>0.07468495695299399</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001109475188260492</v>
+        <v>4.90007172710323e-06</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.316892979397167</v>
+        <v>0.07468164994199294</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.084679245926485e-05</v>
+        <v>-2.316202966500303e-07</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3168829285748475</v>
+        <v>0.07467625005722628</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.068162807157762e-05</v>
+        <v>-2.048134647694879e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3168934145653651</v>
+        <v>0.07467257263099356</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.331395303104609e-05</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386750013692762</v>
+        <v>0.04456170319311439</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3168902537281362</v>
+        <v>0.07466775200041058</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.854216248520305e-06</v>
+        <v>-4.000906869214822e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3168846050064885</v>
+        <v>0.07466269015948591</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>8.273743591478215e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3168826815304042</v>
+        <v>0.07466297054920067</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.844180684889389e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311445</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3168769952528188</v>
+        <v>0.07466285687769461</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.084302348447695e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3168715847829012</v>
+        <v>0.07466272047188761</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3168667501485827</v>
+        <v>0.07466280383099197</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3168666061646752</v>
+        <v>0.07466265984708444</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931144</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3168665834303738</v>
+        <v>0.07466263711278304</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3168669017105906</v>
+        <v>0.0746629553929998</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3168679929570474</v>
+        <v>0.07466404663945665</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3168673033499115</v>
+        <v>0.0746633570323207</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3168673336623132</v>
+        <v>0.0746633873447224</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311445</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3168671442098031</v>
+        <v>0.0746631978922123</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.316867197256506</v>
+        <v>0.07466325093891518</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3168672503032088</v>
+        <v>0.07466330398561806</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3168672124127068</v>
+        <v>0.07466326609511603</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3168670835850002</v>
+        <v>0.07466313726740936</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3168669396010926</v>
+        <v>0.07466299328350183</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3168667804609842</v>
+        <v>0.07466283414339343</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3168668335076871</v>
+        <v>0.07466288719009631</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3168667804609842</v>
+        <v>0.07466283414339343</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3168667804609842</v>
+        <v>0.07466283414339343</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3168665985865747</v>
+        <v>0.07466265226898389</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3168667653047834</v>
+        <v>0.07466281898719258</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3168669623353937</v>
+        <v>0.07466301601780299</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3168668031952854</v>
+        <v>0.07466285687769461</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3168668410857874</v>
+        <v>0.07466289476819662</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3168670381163975</v>
+        <v>0.0746630917988068</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3168670153820964</v>
+        <v>0.07466306906450564</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3168668638200886</v>
+        <v>0.07466291750249779</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3168667880390845</v>
+        <v>0.07466284172149375</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3168668865543897</v>
+        <v>0.07466294023679895</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.31686689413249</v>
+        <v>0.07466294781489927</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.316867159366004</v>
+        <v>0.07466321304841317</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3168668638200886</v>
+        <v>0.07466291750249779</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3168671063193013</v>
+        <v>0.07466316000171053</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3168671896784057</v>
+        <v>0.07466324336081487</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3168670229601969</v>
+        <v>0.07466307664260617</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3168672124127068</v>
+        <v>0.07466326609511603</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3168668638200886</v>
+        <v>0.07466291750249779</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3168666592113779</v>
+        <v>0.07466271289378708</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3168667728828839</v>
+        <v>0.07466282656529313</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3168667880390845</v>
+        <v>0.07466284172149375</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3168665531179723</v>
+        <v>0.07466260680038156</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3168666137427755</v>
+        <v>0.07466266742518474</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3168664849150689</v>
+        <v>0.07466253859747807</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3168666213208758</v>
+        <v>0.07466267500328505</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3168667956171851</v>
+        <v>0.0746628492995943</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3168669396010926</v>
+        <v>0.07466299328350183</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3168667728828839</v>
+        <v>0.07466282656529313</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3168667653047834</v>
+        <v>0.07466281898719258</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3168664773369683</v>
+        <v>0.07466253101937752</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3168664924931692</v>
+        <v>0.07466254617557838</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.316866719836181</v>
+        <v>0.07466277351859026</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3168667046799802</v>
+        <v>0.07466275836238941</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3168668107733857</v>
+        <v>0.07466286445579491</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3168665379617715</v>
+        <v>0.07466259164418071</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3168666364770767</v>
+        <v>0.07466269015948591</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3168667880390845</v>
+        <v>0.07466284172149375</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3168668031952854</v>
+        <v>0.07466285687769461</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3168667804609842</v>
+        <v>0.07466283414339343</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3168668638200886</v>
+        <v>0.07466291750249779</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3168669623353937</v>
+        <v>0.07466301601780299</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3168667956171851</v>
+        <v>0.0746628492995943</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3168667804609842</v>
+        <v>0.07466283414339343</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3168667501485827</v>
+        <v>0.07466280383099197</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3168667349923819</v>
+        <v>0.07466278867479111</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3168667728828839</v>
+        <v>0.07466282656529313</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3168667880390845</v>
+        <v>0.07466284172149375</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3168667804609842</v>
+        <v>0.07466283414339343</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000007.xlsx
+++ b/out/Attention-mamba2_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02221560478210449</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.72</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01715702190995216</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6160766030030931</v>
+        <v>-0.72</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0281473845243454</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.4252234697341919</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.303252637386322</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.09937486052513123</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0005792826414108276</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.05023299902677536</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02583237737417221</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.04001612216234207</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01657959073781967</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002760440111160278</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.04042819142341614</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4160766030030931</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0417177751660347</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.076714909199301</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.1272002458572388</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.05227074027061462</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.05072248727083206</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0251680314540863</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0844016894698143</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.06574922055006027</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1304811537265778</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.3679583966732025</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1743227243423462</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.07341906428337097</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.03798194974660873</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.02197306603193283</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002450212836265564</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0806661918759346</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.07584606856107712</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.076714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.03456152230501175</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001053392887115479</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.01749336719512939</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.02623149007558823</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.076714909199301</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.03116725385189056</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3182757198810577</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.3042474091053009</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.2458189725875854</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.1773441135883331</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.056051339837722e-06</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.03043670499242308</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.1633898168802261</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.06091719527034532</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.004560887590957888</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.1635923385620117</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.03956454121573164</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.005703547543501493</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.09164036065340042</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.04641139676590881</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.008178153438887448</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0957392081618309</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.05706661903728824</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.008749296763472815</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.09762681275606155</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06638754706979776</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.009272762305562895</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.06807074695825577</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.07618430470531061</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.004181882781166383</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.08431901782751083</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.07526914200423401</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.002016429868951753</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02365908026695251</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.07511878078328887</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0009587643781952644</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0590897798538208</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2445617031931145</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.07501730829134468</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0002805572939597059</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.006649576127529144</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2445617031931145</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.07461883747746213</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0001834046270923276</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01890546828508377</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.07470593202662747</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>9.142760150863396e-05</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.09109209477901459</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.07470529328643065</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>4.432644473555205e-05</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.04669258743524551</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.07470248394670594</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>1.392212292957465e-05</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.04131954908370972</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.07468495695299399</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>4.90007172710323e-06</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0966162234544754</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.07468164994199294</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-2.316202966500303e-07</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.1160328537225723</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.07467625005722628</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-2.048134647694879e-06</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.1035795509815216</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.07467257263099356</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.1018925756216049</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.04456170319311439</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.07466775200041058</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-4.000906869214822e-06</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.03489146754145622</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.07466269015948591</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.04360256344079971</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.07466297054920067</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.07996252179145813</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.04456170319311445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.07466285687769461</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.1096929311752319</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.07466272047188761</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.08803896605968475</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.07466280383099197</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.07392752170562744</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.07466265984708444</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.02701670676469803</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2445617031931144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.07466263711278304</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.05140911787748337</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.0746629553929998</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.07079237699508667</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.07466404663945665</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.05564331263303757</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.0746633570323207</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0253290981054306</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.0746633873447224</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.0008962303400039673</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.04456170319311445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.0746631978922123</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.04960630834102631</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.07466325093891518</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.1136460304260254</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.07466330398561806</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.1152176409959793</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.07466326609511603</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.1158282607793808</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.07466313726740936</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.1158369779586792</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.07466299328350183</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.1200810968875885</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.07466283414339343</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.118447333574295</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.07466288719009631</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.08724568784236908</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.07466283414339343</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.1159142851829529</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.07466283414339343</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.10710608959198</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.07466265226898389</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.09703713655471802</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.07466281898719258</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.1204259395599365</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.07466301601780299</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.09295396506786346</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.07466285687769461</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.1144334673881531</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.07466289476819662</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.06660644710063934</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.0746630917988068</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.1148083508014679</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.07466306906450564</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.1091515272855759</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.07466291750249779</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.1032406240701675</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.07466284172149375</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.1169967800378799</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.07466294023679895</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.08929389715194702</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.07466294781489927</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.104207307100296</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.07466321304841317</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.122011661529541</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.07466291750249779</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.1046311557292938</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.07466316000171053</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.12071892619133</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.07466324336081487</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.002163596451282501</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.07466307664260617</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.04205472022294998</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.07466326609511603</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.1007039248943329</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.07466291750249779</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.09873232245445251</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.07466271289378708</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.07687889039516449</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.07466282656529313</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.1147861480712891</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.07466284172149375</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.1172164380550385</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.07466260680038156</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.08779497444629669</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.07466266742518474</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.04799593985080719</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.07466253859747807</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.07113181054592133</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.07466267500328505</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.1199458539485931</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.0746628492995943</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.1019650250673294</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.07466299328350183</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.1121920645236969</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.07466282656529313</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.1165269315242767</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.07466281898719258</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06461967527866364</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.07466253101937752</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.04212053120136261</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.07466254617557838</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.05813038349151611</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.07466277351859026</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.1042027771472931</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.07466275836238941</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.06991921365261078</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.07466286445579491</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.03711292147636414</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.07466259164418071</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.05785089731216431</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.07466269015948591</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.07518230378627777</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.07466284172149375</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.07089975476264954</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.07466285687769461</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.08695566654205322</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.07466283414339343</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.1079849302768707</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.07466291750249779</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0685323029756546</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.07466301601780299</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.05422180891036987</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.0746628492995943</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.05864177644252777</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.07466283414339343</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.07822738587856293</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.07466280383099197</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.07957908511161804</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.07466278867479111</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.06085723638534546</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.07466282656529313</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.09345726668834686</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.6500000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.07466284172149375</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.1325919032096863</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.07466283414339343</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000007.xlsx
+++ b/out/Attention-mamba2_repeat_2_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.02221560478210449</v>
+        <v>-0.02223022654652596</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.72</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.01715702190995216</v>
+        <v>-0.01717023923993111</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.72</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.0281473845243454</v>
+        <v>0.02811836451292038</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.4252234697341919</v>
+        <v>-0.4250859916210175</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.303252637386322</v>
+        <v>-0.3032501339912415</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.09937486052513123</v>
+        <v>-0.09939992427825928</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0005792826414108276</v>
+        <v>0.0005463361740112305</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.05023299902677536</v>
+        <v>-0.05025821179151535</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.02583237737417221</v>
+        <v>-0.0258651003241539</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.04001612216234207</v>
+        <v>-0.040044866502285</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.01657959073781967</v>
+        <v>-0.01660993695259094</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.002760440111160278</v>
+        <v>0.002726636826992035</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.04042819142341614</v>
+        <v>-0.04045810177922249</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0417177751660347</v>
+        <v>-0.0417543388903141</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.2599999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.1272002458572388</v>
+        <v>-0.1272190660238266</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.05227074027061462</v>
+        <v>-0.0523056760430336</v>
       </c>
       <c r="JB17" t="n">
         <v>0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.05072248727083206</v>
+        <v>-0.05075377970933914</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0251680314540863</v>
+        <v>-0.02520567923784256</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0844016894698143</v>
+        <v>-0.0844293087720871</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.06574922055006027</v>
+        <v>-0.06578537821769714</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.02000000000000007</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1304811537265778</v>
+        <v>-0.1305120587348938</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.3679583966732025</v>
+        <v>-0.3679351210594177</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1743227243423462</v>
+        <v>-0.174343153834343</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.07341906428337097</v>
+        <v>-0.07344812899827957</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.03798194974660873</v>
+        <v>-0.03801213577389717</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.02197306603193283</v>
+        <v>-0.02200225740671158</v>
       </c>
       <c r="JB27" t="n">
         <v>0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.002450212836265564</v>
+        <v>0.002414509654045105</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0806661918759346</v>
+        <v>-0.08069051802158356</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.07584606856107712</v>
+        <v>-0.07587157189846039</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.03456152230501175</v>
+        <v>-0.0345899872481823</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.001053392887115479</v>
+        <v>0.001023031771183014</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.01749336719512939</v>
+        <v>-0.01752252876758575</v>
       </c>
       <c r="JB33" t="n">
         <v>0.8599999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.02623149007558823</v>
+        <v>-0.02626209706068039</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.03116725385189056</v>
+        <v>-0.0312073789536953</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3182757198810577</v>
+        <v>-0.3182531893253326</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.3042474091053009</v>
+        <v>-0.3040726184844971</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.2458189725875854</v>
+        <v>-0.245587944984436</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.1773441135883331</v>
+        <v>-0.1770927011966705</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.1633898168802261</v>
+        <v>-0.1631341874599457</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.1635923385620117</v>
+        <v>-0.1633382141590118</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.09164036065340042</v>
+        <v>-0.09159202128648758</v>
       </c>
       <c r="JB42" t="n">
         <v>0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0957392081618309</v>
+        <v>-0.09568356722593307</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.09762681275606155</v>
+        <v>-0.09757128357887268</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.06807074695825577</v>
+        <v>-0.06804715842008591</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.08431901782751083</v>
+        <v>-0.08426231145858765</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.02365908026695251</v>
+        <v>0.0236147940158844</v>
       </c>
       <c r="JB47" t="n">
         <v>0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0590897798538208</v>
+        <v>-0.05904880166053772</v>
       </c>
       <c r="JB48" t="n">
         <v>0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.006649576127529144</v>
+        <v>0.006620295345783234</v>
       </c>
       <c r="JB49" t="n">
         <v>0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01890546828508377</v>
+        <v>0.01890099048614502</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.09109209477901459</v>
+        <v>0.09104305505752563</v>
       </c>
       <c r="JB51" t="n">
         <v>0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.04669258743524551</v>
+        <v>0.04668527841567993</v>
       </c>
       <c r="JB52" t="n">
         <v>0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.04131954908370972</v>
+        <v>0.04130878299474716</v>
       </c>
       <c r="JB53" t="n">
         <v>0.3999999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.0966162234544754</v>
+        <v>0.09658145904541016</v>
       </c>
       <c r="JB54" t="n">
         <v>0.3999999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.1160328537225723</v>
+        <v>0.1159896552562714</v>
       </c>
       <c r="JB55" t="n">
         <v>0.3999999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.1035795509815216</v>
+        <v>0.103533998131752</v>
       </c>
       <c r="JB56" t="n">
         <v>0.2599999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1018925756216049</v>
+        <v>0.1018159091472626</v>
       </c>
       <c r="JB57" t="n">
         <v>0.1199999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.03489146754145622</v>
+        <v>-0.03485093265771866</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.02000000000000007</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.04360256344079971</v>
+        <v>-0.04331254959106445</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.02000000000000007</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.07996252179145813</v>
+        <v>0.07991959154605865</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.1096929311752319</v>
+        <v>0.1096458435058594</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.02000000000000007</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.08803896605968475</v>
+        <v>0.08801409602165222</v>
       </c>
       <c r="JB62" t="n">
         <v>0.1199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.07392752170562744</v>
+        <v>0.07390403747558594</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.02701670676469803</v>
+        <v>0.02701306343078613</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.05140911787748337</v>
+        <v>-0.05135677754878998</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.07079237699508667</v>
+        <v>-0.07073362171649933</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.05564331263303757</v>
+        <v>-0.05561955645680428</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.8599999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0253290981054306</v>
+        <v>-0.02462153136730194</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.5799999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.0008962303400039673</v>
+        <v>0.0008871927857398987</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.3</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.04960630834102631</v>
+        <v>0.04957102239131927</v>
       </c>
       <c r="JB70" t="n">
         <v>0.5799999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1136460304260254</v>
+        <v>0.1135977506637573</v>
       </c>
       <c r="JB71" t="n">
         <v>0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1152176409959793</v>
+        <v>0.1151686310768127</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1158282607793808</v>
+        <v>0.1157889664173126</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.1158369779586792</v>
+        <v>0.11579829454422</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1200810968875885</v>
+        <v>0.1200374960899353</v>
       </c>
       <c r="JB75" t="n">
         <v>0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.118447333574295</v>
+        <v>0.1183944642543793</v>
       </c>
       <c r="JB76" t="n">
         <v>0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.08724568784236908</v>
+        <v>0.08719520270824432</v>
       </c>
       <c r="JB77" t="n">
         <v>0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1159142851829529</v>
+        <v>0.1158706247806549</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.02000000000000007</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.10710608959198</v>
+        <v>0.1070786118507385</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.02000000000000007</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.09703713655471802</v>
+        <v>0.09701117873191833</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.1204259395599365</v>
+        <v>0.1203741431236267</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.09295396506786346</v>
+        <v>0.09289991855621338</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.1144334673881531</v>
+        <v>0.1144005209207535</v>
       </c>
       <c r="JB83" t="n">
         <v>0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.06660644710063934</v>
+        <v>0.0665954053401947</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1148083508014679</v>
+        <v>0.1147649586200714</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.1091515272855759</v>
+        <v>0.1090990006923676</v>
       </c>
       <c r="JB86" t="n">
         <v>0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.1032406240701675</v>
+        <v>0.1031912267208099</v>
       </c>
       <c r="JB87" t="n">
         <v>0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.1169967800378799</v>
+        <v>0.1169475764036179</v>
       </c>
       <c r="JB88" t="n">
         <v>0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.08929389715194702</v>
+        <v>0.08927860856056213</v>
       </c>
       <c r="JB89" t="n">
         <v>0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.104207307100296</v>
+        <v>0.1041731834411621</v>
       </c>
       <c r="JB90" t="n">
         <v>0.8599999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.122011661529541</v>
+        <v>0.1219590753316879</v>
       </c>
       <c r="JB91" t="n">
         <v>0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.1046311557292938</v>
+        <v>0.1045997887849808</v>
       </c>
       <c r="JB92" t="n">
         <v>0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.12071892619133</v>
+        <v>0.1206593364477158</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.002163596451282501</v>
+        <v>0.002435751259326935</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.04205472022294998</v>
+        <v>0.04203666746616364</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.1007039248943329</v>
+        <v>0.100662499666214</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.09873232245445251</v>
+        <v>0.09867647290229797</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.07687889039516449</v>
+        <v>0.0768299400806427</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.1600000000000001</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1147861480712891</v>
+        <v>0.1147407740354538</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.1172164380550385</v>
+        <v>0.1171618103981018</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.08779497444629669</v>
+        <v>0.08773890137672424</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.04799593985080719</v>
+        <v>0.0479389876127243</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.07113181054592133</v>
+        <v>0.07111258804798126</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1199458539485931</v>
+        <v>0.1198905408382416</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1019650250673294</v>
+        <v>0.1019147932529449</v>
       </c>
       <c r="JB105" t="n">
         <v>0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1121920645236969</v>
+        <v>0.1121440827846527</v>
       </c>
       <c r="JB106" t="n">
         <v>0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.1165269315242767</v>
+        <v>0.1164691150188446</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06461967527866364</v>
+        <v>0.06456992030143738</v>
       </c>
       <c r="JB108" t="n">
         <v>0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.04212053120136261</v>
+        <v>0.04207997769117355</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.05813038349151611</v>
+        <v>0.05808686465024948</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.1042027771472931</v>
+        <v>0.1041439473628998</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.06991921365261078</v>
+        <v>0.06986744701862335</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.03711292147636414</v>
+        <v>0.03707350790500641</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.05785089731216431</v>
+        <v>0.05780602246522903</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.07518230378627777</v>
+        <v>0.07513253390789032</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.07089975476264954</v>
+        <v>0.07085341215133667</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.5799999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.08695566654205322</v>
+        <v>0.08690765500068665</v>
       </c>
       <c r="JB117" t="n">
         <v>0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.1079849302768707</v>
+        <v>0.107926219701767</v>
       </c>
       <c r="JB118" t="n">
         <v>0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.0685323029756546</v>
+        <v>0.06848274171352386</v>
       </c>
       <c r="JB119" t="n">
         <v>0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.05422180891036987</v>
+        <v>0.05417637526988983</v>
       </c>
       <c r="JB120" t="n">
         <v>0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.05864177644252777</v>
+        <v>0.05859728902578354</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.07822738587856293</v>
+        <v>0.07817786931991577</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.1199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.07957908511161804</v>
+        <v>0.07952742278575897</v>
       </c>
       <c r="JB123" t="n">
         <v>0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.06085723638534546</v>
+        <v>0.06081428378820419</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.09345726668834686</v>
+        <v>0.09340880811214447</v>
       </c>
       <c r="JB125" t="n">
         <v>0.6500000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.1325919032096863</v>
+        <v>0.132542222738266</v>
       </c>
       <c r="JB126" t="n">
         <v>0.8600000000000001</v>
